--- a/Data/MH_StruggleofSwaraj.xlsx
+++ b/Data/MH_StruggleofSwaraj.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,961 +472,961 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which movement began as a reaction to the Partition of Bengal in 1905?</t>
+          <t>Who was the Viceroy of India during the Jallianwala Bagh massacre?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Lord Hardinge</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bengal was divided by the British, sparking a boycott and nationalistic movement.</t>
+          <t>He was the British Governor-General when the tragedy occurred</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Who was associated with the foundation of the Home Rule League in 1916?</t>
+          <t>Which movement first used mass mobilization in India?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Home Rule Movement</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>He started the league to demand self-government.</t>
+          <t>In protest of partition of Bengal 1905</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Lucknow Pact of 1916 was signed between which two political groups?</t>
+          <t>Which of the following was *not* a feature of Montagu-Chelmsford reforms?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Congress and British</t>
+          <t>Introduction of Dyarchy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Congress and Muslim League</t>
+          <t>Bicameral Legislature</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Muslim League and British</t>
+          <t>Abolition of ICS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Congress and Home Rule League</t>
+          <t>Expansion of legislative councils</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Congress and Muslim League</t>
+          <t>Abolition of ICS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>It was a historic agreement for Hindu-Muslim unity.</t>
+          <t>ICS was not abolished.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which act allowed the British government to imprison people without trial in 1919?</t>
+          <t>Which movement was suspended after the Chauri Chaura incident?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Government of India Act 1919</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Defence of India Act</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>It curtailed civil liberties and was opposed widely.</t>
+          <t>Gandhi called off the movement due to violence</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who termed the Montagu-Chelmsford Reforms as “unworthy of England to offer and India to accept”?</t>
+          <t>Who wrote the book ‘Hind Swaraj’?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Gopal Krishna Gokhale</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Annie Besant</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mahatma Gandhi</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Mahatma Gandhi</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Annie Besant</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lala Lajpat Rai</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Mahatma Gandhi</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>He criticized the reforms for being inadequate.</t>
+          <t>He outlined his vision of self-rule.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who led the extremist faction during the split at the Surat session of Congress in 1907?</t>
+          <t>Which movement began as a reaction to the Partition of Bengal in 1905?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motilal Nehru</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The extremists wanted aggressive methods for freedom.</t>
+          <t>Bengal was divided by the British, sparking a boycott and nationalistic movement.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What was the main objective of the Swadeshi Movement?</t>
+          <t>Who presided over the Indian National Congress session in 1906 and gave the call for “Swaraj”?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>To demand Dominion status</t>
+          <t>Dada Bhai Naoroji</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To boycott British goods and promote Indian industries</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>To demand reservation</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>To oppose the salt tax</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>To boycott British goods and promote Indian industries</t>
+          <t>Dada Bhai Naoroji</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>It aimed at economic self-reliance.</t>
+          <t>He officially demanded self-rule.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which British official was assassinated by Madan Lal Dhingra in London (1909)?</t>
+          <t>Which of these was NOT a demand of the Congress in the early 20th century?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lord Hardinge</t>
+          <t>Dominion status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Curzon Wyllie</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lord Minto</t>
+          <t>Civil rights</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>General Dyer</t>
+          <t>Reduction of military expenditure</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curzon Wyllie</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>This was an early act of revolutionary nationalism.</t>
+          <t>This became a goal only after 1929</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The All India Home Rule League was founded in 1916 by</t>
+          <t>The slogan 'Swaraj is my birthright' was given by?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Motilal Nehru</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Both worked parallelly for the same cause.</t>
+          <t>Assertive nationalist leader who inspired the youth</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which revolutionaries were involved in the Alipore Bomb case (1908)?</t>
+          <t>Which Congress leader was known as the 'Lion of Punjab'?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bhagat Singh and Rajguru</t>
+          <t>Bhagat Singh</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aurobindo Ghosh and his brother</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mangal Pandey and Azad</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bose and Dhingra</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aurobindo Ghosh and his brother</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>They were accused of planning a bomb attack on a British judge.</t>
+          <t>For his fiery speeches and nationalism</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The ‘Moderates’ and ‘Extremists’ of Congress reunited in which session?</t>
+          <t>Which act increased the number of Indians in the legislative council in 1909?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Surat Session 1907</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lucknow Session 1916</t>
+          <t>Montagu Reforms</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Calcutta Session 1906</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Indian Councils Act</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lucknow Session 1916</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>A key unity moment in the freedom struggle.</t>
+          <t>Also introduced separate electorates for Muslims.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The partition of Bengal was annulled in which year?</t>
+          <t>Which group was most influenced by socialist ideas during the freedom struggle?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>Muslim League</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Due to mass opposition, the British reversed the decision.</t>
+          <t>Subhas Bose was heavily inspired by socialism</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What was the purpose of the Montagu Declaration of 1917?</t>
+          <t>Who led the extremist faction during the split at the Surat session of Congress in 1907?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Indianization of Army</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Increasing salaries of officials</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gradual development of self-government</t>
+          <t>Motilal Nehru</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gradual development of self-government</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A vague promise made by the British.</t>
+          <t>The extremists wanted aggressive methods for freedom.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which movement marked Mahatma Gandhi’s first active involvement in Indian politics?</t>
+          <t>Which party did Subhas Chandra Bose form after resigning from Congress?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rowlatt Satyagraha</t>
+          <t>Ghadar Party</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kheda Satyagraha</t>
+          <t>Swaraj Party</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dandi March</t>
+          <t>Indian National Army</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>He fought for the rights of indigo farmers.</t>
+          <t>Formed to continue revolutionary methods</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which organization aimed to promote political education and demand self-rule in India?</t>
+          <t>Which was the last major movement before India’s independence?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arya Samaj</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Muslim League</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Home Rule League</t>
+          <t>Non-Cooperation</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Indian National Army</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Home Rule League</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>It educated people on political rights.</t>
+          <t>Launched in 1942 demanding end of British rule</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who wrote the book ‘Hind Swaraj’?</t>
+          <t>The ‘extremists’ within Congress used which of the following strategies?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Petitions</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Peaceful protests</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Constitutional methods</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Boycott and Swadeshi</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Boycott and Swadeshi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>He outlined his vision of self-rule.</t>
+          <t>They rejected soft methods of the moderates.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Jallianwala Bagh massacre took place in which year?</t>
+          <t>In which year was the Non-Cooperation Movement launched?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>1920</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1919</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>This tragic event shook the nation and turned the tide.</t>
+          <t>Started by Gandhi to oppose Rowlatt Act and Jallianwala Bagh massacre</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who presided over the Indian National Congress session in 1906 and gave the call for “Swaraj”?</t>
+          <t>The Jallianwala Bagh massacre took place in which year?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dada Bhai Naoroji</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dada Bhai Naoroji</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>He officially demanded self-rule.</t>
+          <t>This tragic event shook the nation and turned the tide.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which leader was associated with the extremist school of thought?</t>
+          <t>Who was associated with the foundation of the Home Rule League in 1916?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Subhash Chandra Bose</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>He believed "Swaraj is my birthright."</t>
+          <t>He started the league to demand self-government.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which act increased the number of Indians in the legislative council in 1909?</t>
+          <t>Which leader was associated with the extremist school of thought?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Montagu Reforms</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Indian Councils Act</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Also introduced separate electorates for Muslims.</t>
+          <t>He believed "Swaraj is my birthright."</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What was the main demand of the Home Rule League?</t>
+          <t>What was the main objective of the Swadeshi Movement?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Complete Independence</t>
+          <t>To demand Dominion status</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Religious reforms</t>
+          <t>To boycott British goods and promote Indian industries</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Social equality</t>
+          <t>To demand reservation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Self-government within British Empire</t>
+          <t>To oppose the salt tax</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Self-government within British Empire</t>
+          <t>To boycott British goods and promote Indian industries</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>It was a moderate demand for autonomy.</t>
+          <t>It aimed at economic self-reliance.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Who was the first woman president of Indian National Congress?</t>
+          <t>Which movement marked Mahatma Gandhi’s first active involvement in Indian politics?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Rowlatt Satyagraha</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Kheda Satyagraha</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vijaya Lakshmi Pandit</t>
+          <t>Dandi March</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>She became president in 1917.</t>
+          <t>He fought for the rights of indigo farmers.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which agreement helped unite Hindus and Muslims for a common political goal in 1916?</t>
+          <t>What was the main aim of the Simon Commission?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poona Pact</t>
+          <t>To partition Bengal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Delhi Pact</t>
+          <t>To assess the working of Government of India Act 1919</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lucknow Pact</t>
+          <t>To introduce Purna Swaraj</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Simla Agreement</t>
+          <t>To suppress revolutionaries</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lucknow Pact</t>
+          <t>To assess the working of Government of India Act 1919</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>It was a rare moment of unity.</t>
+          <t>Sent by British without Indian members</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which of the following was *not* a feature of Montagu-Chelmsford reforms?</t>
+          <t>Which event led to Gandhi’s entry into Indian politics?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Introduction of Dyarchy</t>
+          <t>Jallianwala Bagh</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bicameral Legislature</t>
+          <t>Champaran Satyagraha</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Abolition of ICS</t>
+          <t>Khilafat Movement</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Expansion of legislative councils</t>
+          <t>Simon Commission</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Abolition of ICS</t>
+          <t>Champaran Satyagraha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ICS was not abolished.</t>
+          <t>To address indigo farmers' plight</t>
         </is>
       </c>
     </row>
@@ -1436,117 +1436,117 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The ‘extremists’ within Congress used which of the following strategies?</t>
+          <t>Who gave the slogan “Do or Die” during the Quit India Movement?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Petitions</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Peaceful protests</t>
+          <t>Bose</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Constitutional methods</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Boycott and Swadeshi</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Boycott and Swadeshi</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>They rejected soft methods of the moderates.</t>
+          <t>Urged Indians to fight for freedom at all costs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Who launched the Home Rule League in 1916?</t>
+          <t>The ‘Moderates’ and ‘Extremists’ of Congress reunited in which session?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Surat Session 1907</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Lucknow Session 1916</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Calcutta Session 1906</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Lucknow Session 1916</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>To advocate self-government within British India</t>
+          <t>A key unity moment in the freedom struggle.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Who was the Viceroy of India during the Jallianwala Bagh massacre?</t>
+          <t>Who termed the Montagu-Chelmsford Reforms as “unworthy of England to offer and India to accept”?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lord Hardinge</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>He was the British Governor-General when the tragedy occurred</t>
+          <t>He criticized the reforms for being inadequate.</t>
         </is>
       </c>
     </row>
@@ -1556,917 +1556,917 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which act gave Indians limited role in the administration for the first time?</t>
+          <t>The Lucknow Pact of 1916 was signed between which two political groups?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Congress and British</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1861</t>
+          <t>Congress and Muslim League</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1892</t>
+          <t>Muslim League and British</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Congress and Home Rule League</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Congress and Muslim League</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Also known as Morley-Minto Reforms, introduced separate electorates</t>
+          <t>It was a historic agreement for Hindu-Muslim unity.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Who founded the Swaraj Party in 1923?</t>
+          <t>Which organization aimed to promote political education and demand self-rule in India?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gandhi and Nehru</t>
+          <t>Arya Samaj</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Motilal Nehru and C.R. Das</t>
+          <t>Muslim League</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Home Rule League</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose and Rajendra Prasad</t>
+          <t>Indian National Army</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Motilal Nehru and C.R. Das</t>
+          <t>Home Rule League</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>They wanted to enter legislative councils and wreck them from within</t>
+          <t>It educated people on political rights.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which session of Congress declared Purna Swaraj as the goal?</t>
+          <t>Who was the first woman president of Indian National Congress?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bombay Session 1918</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Calcutta Session 1920</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nagpur Session 1921</t>
+          <t>Vijaya Lakshmi Pandit</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>It declared complete independence as the goal of INC</t>
+          <t>She became president in 1917.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>In which year was the Non-Cooperation Movement launched?</t>
+          <t>Which British official was assassinated by Madan Lal Dhingra in London (1909)?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Lord Hardinge</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Curzon Wyllie</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>Lord Minto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>General Dyer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Curzon Wyllie</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Started by Gandhi to oppose Rowlatt Act and Jallianwala Bagh massacre</t>
+          <t>This was an early act of revolutionary nationalism.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which movement was suspended after the Chauri Chaura incident?</t>
+          <t>Which revolutionaries were involved in the Alipore Bomb case (1908)?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Bhagat Singh and Rajguru</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Aurobindo Ghosh and his brother</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Mangal Pandey and Azad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Bose and Dhingra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Aurobindo Ghosh and his brother</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Gandhi called off the movement due to violence</t>
+          <t>They were accused of planning a bomb attack on a British judge.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What was the main aim of the Simon Commission?</t>
+          <t>Which session of Congress declared Purna Swaraj as the goal?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>To partition Bengal</t>
+          <t>Bombay Session 1918</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To assess the working of Government of India Act 1919</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>To introduce Purna Swaraj</t>
+          <t>Calcutta Session 1920</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>To suppress revolutionaries</t>
+          <t>Nagpur Session 1921</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>To assess the working of Government of India Act 1919</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sent by British without Indian members</t>
+          <t>It declared complete independence as the goal of INC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who wrote ‘Hind Swaraj’?</t>
+          <t>What was the outcome of the Gandhi-Irwin Pact?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>British granted independence</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Salt law repealed</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>End of Civil Disobedience temporarily</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Constitution formed</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>End of Civil Disobedience temporarily</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Book advocating self-rule and non-violence</t>
+          <t>Also allowed peaceful picketing</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which British official was assassinated in retaliation of the Jallianwala Bagh massacre?</t>
+          <t>Which act introduced provincial autonomy?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Michael O’Dwyer</t>
+          <t>Government of India Act 1919</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Government of India Act 1935</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Indian Independence Act 1947</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Michael O’Dwyer</t>
+          <t>Government of India Act 1935</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>He ordered Dyer’s actions and was killed by Udham Singh</t>
+          <t>Allowed provinces more control in governance</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Congress leader was known as the 'Lion of Punjab'?</t>
+          <t>What was the main demand of the Home Rule League?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bhagat Singh</t>
+          <t>Complete Independence</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Religious reforms</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Social equality</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Self-government within British Empire</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Self-government within British Empire</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>For his fiery speeches and nationalism</t>
+          <t>It was a moderate demand for autonomy.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The slogan 'Swaraj is my birthright' was given by?</t>
+          <t>When was the Civil Disobedience Movement relaunched after suspension?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Assertive nationalist leader who inspired the youth</t>
+          <t>Due to failure of Round Table Conferences</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which movement first used mass mobilization in India?</t>
+          <t>Who launched the Home Rule League in 1916?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Home Rule Movement</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>In protest of partition of Bengal 1905</t>
+          <t>To advocate self-government within British India</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Who was the Governor-General during the First Round Table Conference?</t>
+          <t>Which agreement helped unite Hindus and Muslims for a common political goal in 1916?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Poona Pact</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lord Willingdon</t>
+          <t>Delhi Pact</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Lucknow Pact</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lord Wavell</t>
+          <t>Simla Agreement</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Lucknow Pact</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>It was held in London in 1930</t>
+          <t>It was a rare moment of unity.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which party did Subhas Chandra Bose form after resigning from Congress?</t>
+          <t>Which British official was assassinated in retaliation of the Jallianwala Bagh massacre?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ghadar Party</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Swaraj Party</t>
+          <t>Michael O’Dwyer</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Indian National Army</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Michael O’Dwyer</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Formed to continue revolutionary methods</t>
+          <t>He ordered Dyer’s actions and was killed by Udham Singh</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which of these was NOT a demand of the Congress in the early 20th century?</t>
+          <t>Which leader was associated with the extremist faction of Congress?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dominion status</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Civil rights</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reduction of military expenditure</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>This became a goal only after 1929</t>
+          <t>Believed in assertive and confrontational methods</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which leader was associated with the extremist faction of Congress?</t>
+          <t>The partition of Bengal was annulled in which year?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Believed in assertive and confrontational methods</t>
+          <t>Due to mass opposition, the British reversed the decision.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which movement aimed to boycott foreign goods and promote Indian industries?</t>
+          <t>The All India Home Rule League was founded in 1916 by</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quit India</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Non-Cooperation</t>
+          <t>Motilal Nehru</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Civil Disobedience</t>
+          <t>Subhash Chandra Bose</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Focused on economic self-reliance</t>
+          <t>Both worked parallelly for the same cause.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which event led to Gandhi’s entry into Indian politics?</t>
+          <t>Who was the Governor-General during the First Round Table Conference?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jallianwala Bagh</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Champaran Satyagraha</t>
+          <t>Lord Willingdon</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Khilafat Movement</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Simon Commission</t>
+          <t>Lord Wavell</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Champaran Satyagraha</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>To address indigo farmers' plight</t>
+          <t>It was held in London in 1930</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What was the outcome of the Gandhi-Irwin Pact?</t>
+          <t>Who wrote ‘Hind Swaraj’?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>British granted independence</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Salt law repealed</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>End of Civil Disobedience temporarily</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Constitution formed</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>End of Civil Disobedience temporarily</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Also allowed peaceful picketing</t>
+          <t>Book advocating self-rule and non-violence</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>When was the Civil Disobedience Movement relaunched after suspension?</t>
+          <t>Which act gave Indians limited role in the administration for the first time?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>Indian Councils Act 1861</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>Indian Councils Act 1892</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Due to failure of Round Table Conferences</t>
+          <t>Also known as Morley-Minto Reforms, introduced separate electorates</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which group was most influenced by socialist ideas during the freedom struggle?</t>
+          <t>Which act allowed the British government to imprison people without trial in 1919?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Government of India Act 1919</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Muslim League</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Defence of India Act</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Subhas Bose was heavily inspired by socialism</t>
+          <t>It curtailed civil liberties and was opposed widely.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which act introduced provincial autonomy?</t>
+          <t>Which movement aimed to boycott foreign goods and promote Indian industries?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Quit India</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Government of India Act 1919</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Government of India Act 1935</t>
+          <t>Non-Cooperation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Indian Independence Act 1947</t>
+          <t>Civil Disobedience</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Government of India Act 1935</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Allowed provinces more control in governance</t>
+          <t>Focused on economic self-reliance</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which was the last major movement before India’s independence?</t>
+          <t>Who founded the Swaraj Party in 1923?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Gandhi and Nehru</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Motilal Nehru and C.R. Das</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Non-Cooperation</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Subhash Chandra Bose and Rajendra Prasad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Motilal Nehru and C.R. Das</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Launched in 1942 demanding end of British rule</t>
+          <t>They wanted to enter legislative councils and wreck them from within</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Who gave the slogan “Do or Die” during the Quit India Movement?</t>
+          <t>What was the purpose of the Montagu Declaration of 1917?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bose</t>
+          <t>Indianization of Army</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Increasing salaries of officials</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Gradual development of self-government</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Gradual development of self-government</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Urged Indians to fight for freedom at all costs</t>
+          <t>A vague promise made by the British.</t>
         </is>
       </c>
     </row>

--- a/Data/MH_StruggleofSwaraj.xlsx
+++ b/Data/MH_StruggleofSwaraj.xlsx
@@ -472,81 +472,81 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who was the Viceroy of India during the Jallianwala Bagh massacre?</t>
+          <t>Which Congress leader was known as the 'Lion of Punjab'?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Bhagat Singh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lord Hardinge</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>He was the British Governor-General when the tragedy occurred</t>
+          <t>For his fiery speeches and nationalism</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which movement first used mass mobilization in India?</t>
+          <t>Which party did Subhas Chandra Bose form after resigning from Congress?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Ghadar Party</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Swaraj Party</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Home Rule Movement</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Indian National Army</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>In protest of partition of Bengal 1905</t>
+          <t>Formed to continue revolutionary methods</t>
         </is>
       </c>
     </row>
@@ -556,37 +556,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which of the following was *not* a feature of Montagu-Chelmsford reforms?</t>
+          <t>Which was the last major movement before India’s independence?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction of Dyarchy</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bicameral Legislature</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Abolition of ICS</t>
+          <t>Non-Cooperation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Expansion of legislative councils</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Abolition of ICS</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ICS was not abolished.</t>
+          <t>Launched in 1942 demanding end of British rule</t>
         </is>
       </c>
     </row>
@@ -596,942 +596,942 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which movement was suspended after the Chauri Chaura incident?</t>
+          <t>What was the main objective of the Swadeshi Movement?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>To demand Dominion status</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>To boycott British goods and promote Indian industries</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>To demand reservation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>To oppose the salt tax</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>To boycott British goods and promote Indian industries</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Gandhi called off the movement due to violence</t>
+          <t>It aimed at economic self-reliance.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who wrote the book ‘Hind Swaraj’?</t>
+          <t>The partition of Bengal was annulled in which year?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>He outlined his vision of self-rule.</t>
+          <t>Due to mass opposition, the British reversed the decision.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which movement began as a reaction to the Partition of Bengal in 1905?</t>
+          <t>Who wrote the book ‘Hind Swaraj’?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bengal was divided by the British, sparking a boycott and nationalistic movement.</t>
+          <t>He outlined his vision of self-rule.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who presided over the Indian National Congress session in 1906 and gave the call for “Swaraj”?</t>
+          <t>Which group was most influenced by socialist ideas during the freedom struggle?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dada Bhai Naoroji</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Muslim League</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dada Bhai Naoroji</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>He officially demanded self-rule.</t>
+          <t>Subhas Bose was heavily inspired by socialism</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which of these was NOT a demand of the Congress in the early 20th century?</t>
+          <t>Which revolutionaries were involved in the Alipore Bomb case (1908)?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dominion status</t>
+          <t>Bhagat Singh and Rajguru</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Aurobindo Ghosh and his brother</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Civil rights</t>
+          <t>Mangal Pandey and Azad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reduction of military expenditure</t>
+          <t>Bose and Dhingra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Aurobindo Ghosh and his brother</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>This became a goal only after 1929</t>
+          <t>They were accused of planning a bomb attack on a British judge.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The slogan 'Swaraj is my birthright' was given by?</t>
+          <t>Which movement marked Mahatma Gandhi’s first active involvement in Indian politics?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Rowlatt Satyagraha</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Kheda Satyagraha</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Dandi March</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Assertive nationalist leader who inspired the youth</t>
+          <t>He fought for the rights of indigo farmers.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Congress leader was known as the 'Lion of Punjab'?</t>
+          <t>Which of these was NOT a demand of the Congress in the early 20th century?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bhagat Singh</t>
+          <t>Dominion status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Civil rights</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Reduction of military expenditure</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>For his fiery speeches and nationalism</t>
+          <t>This became a goal only after 1929</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which act increased the number of Indians in the legislative council in 1909?</t>
+          <t>Who termed the Montagu-Chelmsford Reforms as “unworthy of England to offer and India to accept”?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Montagu Reforms</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Indian Councils Act</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Also introduced separate electorates for Muslims.</t>
+          <t>He criticized the reforms for being inadequate.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which group was most influenced by socialist ideas during the freedom struggle?</t>
+          <t>The ‘Moderates’ and ‘Extremists’ of Congress reunited in which session?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Surat Session 1907</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Muslim League</t>
+          <t>Lucknow Session 1916</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>Calcutta Session 1906</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Lucknow Session 1916</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Subhas Bose was heavily inspired by socialism</t>
+          <t>A key unity moment in the freedom struggle.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who led the extremist faction during the split at the Surat session of Congress in 1907?</t>
+          <t>Which session of Congress declared Purna Swaraj as the goal?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Bombay Session 1918</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Calcutta Session 1920</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motilal Nehru</t>
+          <t>Nagpur Session 1921</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The extremists wanted aggressive methods for freedom.</t>
+          <t>It declared complete independence as the goal of INC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which party did Subhas Chandra Bose form after resigning from Congress?</t>
+          <t>What was the purpose of the Montagu Declaration of 1917?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ghadar Party</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Swaraj Party</t>
+          <t>Indianization of Army</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Increasing salaries of officials</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Indian National Army</t>
+          <t>Gradual development of self-government</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Gradual development of self-government</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Formed to continue revolutionary methods</t>
+          <t>A vague promise made by the British.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which was the last major movement before India’s independence?</t>
+          <t>The All India Home Rule League was founded in 1916 by</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Non-Cooperation</t>
+          <t>Motilal Nehru</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Subhash Chandra Bose</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Launched in 1942 demanding end of British rule</t>
+          <t>Both worked parallelly for the same cause.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The ‘extremists’ within Congress used which of the following strategies?</t>
+          <t>Which event led to Gandhi’s entry into Indian politics?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petitions</t>
+          <t>Jallianwala Bagh</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Peaceful protests</t>
+          <t>Champaran Satyagraha</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Constitutional methods</t>
+          <t>Khilafat Movement</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Boycott and Swadeshi</t>
+          <t>Simon Commission</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Boycott and Swadeshi</t>
+          <t>Champaran Satyagraha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>They rejected soft methods of the moderates.</t>
+          <t>To address indigo farmers' plight</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>In which year was the Non-Cooperation Movement launched?</t>
+          <t>Which organization aimed to promote political education and demand self-rule in India?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Arya Samaj</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Muslim League</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>Home Rule League</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>Indian National Army</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Home Rule League</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Started by Gandhi to oppose Rowlatt Act and Jallianwala Bagh massacre</t>
+          <t>It educated people on political rights.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Jallianwala Bagh massacre took place in which year?</t>
+          <t>Who led the extremist faction during the split at the Surat session of Congress in 1907?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Motilal Nehru</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>This tragic event shook the nation and turned the tide.</t>
+          <t>The extremists wanted aggressive methods for freedom.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who was associated with the foundation of the Home Rule League in 1916?</t>
+          <t>What was the main aim of the Simon Commission?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>To partition Bengal</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>To assess the working of Government of India Act 1919</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>To introduce Purna Swaraj</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose</t>
+          <t>To suppress revolutionaries</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>To assess the working of Government of India Act 1919</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>He started the league to demand self-government.</t>
+          <t>Sent by British without Indian members</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which leader was associated with the extremist school of thought?</t>
+          <t>The Lucknow Pact of 1916 was signed between which two political groups?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Congress and British</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Congress and Muslim League</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Muslim League and British</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Congress and Home Rule League</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Congress and Muslim League</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>He believed "Swaraj is my birthright."</t>
+          <t>It was a historic agreement for Hindu-Muslim unity.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What was the main objective of the Swadeshi Movement?</t>
+          <t>Who founded the Swaraj Party in 1923?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>To demand Dominion status</t>
+          <t>Gandhi and Nehru</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To boycott British goods and promote Indian industries</t>
+          <t>Motilal Nehru and C.R. Das</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>To demand reservation</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>To oppose the salt tax</t>
+          <t>Subhash Chandra Bose and Rajendra Prasad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>To boycott British goods and promote Indian industries</t>
+          <t>Motilal Nehru and C.R. Das</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>It aimed at economic self-reliance.</t>
+          <t>They wanted to enter legislative councils and wreck them from within</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which movement marked Mahatma Gandhi’s first active involvement in Indian politics?</t>
+          <t>Which leader was associated with the extremist faction of Congress?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rowlatt Satyagraha</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kheda Satyagraha</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dandi March</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>He fought for the rights of indigo farmers.</t>
+          <t>Believed in assertive and confrontational methods</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What was the main aim of the Simon Commission?</t>
+          <t>Which movement was suspended after the Chauri Chaura incident?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>To partition Bengal</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To assess the working of Government of India Act 1919</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>To introduce Purna Swaraj</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>To suppress revolutionaries</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>To assess the working of Government of India Act 1919</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sent by British without Indian members</t>
+          <t>Gandhi called off the movement due to violence</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which event led to Gandhi’s entry into Indian politics?</t>
+          <t>Which movement began as a reaction to the Partition of Bengal in 1905?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jallianwala Bagh</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Champaran Satyagraha</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Khilafat Movement</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Simon Commission</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Champaran Satyagraha</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>To address indigo farmers' plight</t>
+          <t>Bengal was divided by the British, sparking a boycott and nationalistic movement.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Who gave the slogan “Do or Die” during the Quit India Movement?</t>
+          <t>Which act increased the number of Indians in the legislative council in 1909?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bose</t>
+          <t>Montagu Reforms</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Indian Councils Act</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Urged Indians to fight for freedom at all costs</t>
+          <t>Also introduced separate electorates for Muslims.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The ‘Moderates’ and ‘Extremists’ of Congress reunited in which session?</t>
+          <t>When was the Civil Disobedience Movement relaunched after suspension?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Surat Session 1907</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lucknow Session 1916</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Calcutta Session 1906</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lucknow Session 1916</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A key unity moment in the freedom struggle.</t>
+          <t>Due to failure of Round Table Conferences</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Who termed the Montagu-Chelmsford Reforms as “unworthy of England to offer and India to accept”?</t>
+          <t>Who wrote ‘Hind Swaraj’?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>He criticized the reforms for being inadequate.</t>
+          <t>Book advocating self-rule and non-violence</t>
         </is>
       </c>
     </row>
@@ -1556,437 +1556,437 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Lucknow Pact of 1916 was signed between which two political groups?</t>
+          <t>Which act gave Indians limited role in the administration for the first time?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Congress and British</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Congress and Muslim League</t>
+          <t>Indian Councils Act 1861</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Muslim League and British</t>
+          <t>Indian Councils Act 1892</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Congress and Home Rule League</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Congress and Muslim League</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>It was a historic agreement for Hindu-Muslim unity.</t>
+          <t>Also known as Morley-Minto Reforms, introduced separate electorates</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which organization aimed to promote political education and demand self-rule in India?</t>
+          <t>Which of the following was *not* a feature of Montagu-Chelmsford reforms?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arya Samaj</t>
+          <t>Introduction of Dyarchy</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Muslim League</t>
+          <t>Bicameral Legislature</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Home Rule League</t>
+          <t>Abolition of ICS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Indian National Army</t>
+          <t>Expansion of legislative councils</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Home Rule League</t>
+          <t>Abolition of ICS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>It educated people on political rights.</t>
+          <t>ICS was not abolished.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Who was the first woman president of Indian National Congress?</t>
+          <t>The Jallianwala Bagh massacre took place in which year?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vijaya Lakshmi Pandit</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>She became president in 1917.</t>
+          <t>This tragic event shook the nation and turned the tide.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which British official was assassinated by Madan Lal Dhingra in London (1909)?</t>
+          <t>Which act allowed the British government to imprison people without trial in 1919?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lord Hardinge</t>
+          <t>Government of India Act 1919</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Curzon Wyllie</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lord Minto</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>General Dyer</t>
+          <t>Defence of India Act</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Curzon Wyllie</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>This was an early act of revolutionary nationalism.</t>
+          <t>It curtailed civil liberties and was opposed widely.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which revolutionaries were involved in the Alipore Bomb case (1908)?</t>
+          <t>The slogan 'Swaraj is my birthright' was given by?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bhagat Singh and Rajguru</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aurobindo Ghosh and his brother</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mangal Pandey and Azad</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bose and Dhingra</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aurobindo Ghosh and his brother</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>They were accused of planning a bomb attack on a British judge.</t>
+          <t>Assertive nationalist leader who inspired the youth</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which session of Congress declared Purna Swaraj as the goal?</t>
+          <t>Which movement aimed to boycott foreign goods and promote Indian industries?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bombay Session 1918</t>
+          <t>Quit India</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Calcutta Session 1920</t>
+          <t>Non-Cooperation</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nagpur Session 1921</t>
+          <t>Civil Disobedience</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>It declared complete independence as the goal of INC</t>
+          <t>Focused on economic self-reliance</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What was the outcome of the Gandhi-Irwin Pact?</t>
+          <t>Which movement first used mass mobilization in India?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>British granted independence</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Salt law repealed</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>End of Civil Disobedience temporarily</t>
+          <t>Home Rule Movement</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Constitution formed</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>End of Civil Disobedience temporarily</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Also allowed peaceful picketing</t>
+          <t>In protest of partition of Bengal 1905</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which act introduced provincial autonomy?</t>
+          <t>Who was the first woman president of Indian National Congress?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Government of India Act 1919</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Government of India Act 1935</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Indian Independence Act 1947</t>
+          <t>Vijaya Lakshmi Pandit</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Government of India Act 1935</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Allowed provinces more control in governance</t>
+          <t>She became president in 1917.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What was the main demand of the Home Rule League?</t>
+          <t>Who was the Governor-General during the First Round Table Conference?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Complete Independence</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Religious reforms</t>
+          <t>Lord Willingdon</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Social equality</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Self-government within British Empire</t>
+          <t>Lord Wavell</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Self-government within British Empire</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>It was a moderate demand for autonomy.</t>
+          <t>It was held in London in 1930</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>When was the Civil Disobedience Movement relaunched after suspension?</t>
+          <t>What was the outcome of the Gandhi-Irwin Pact?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>British granted independence</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>Salt law repealed</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>End of Civil Disobedience temporarily</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>Constitution formed</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>End of Civil Disobedience temporarily</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Due to failure of Round Table Conferences</t>
+          <t>Also allowed peaceful picketing</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who launched the Home Rule League in 1916?</t>
+          <t>Which agreement helped unite Hindus and Muslims for a common political goal in 1916?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Poona Pact</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Delhi Pact</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Lucknow Pact</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Simla Agreement</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Lucknow Pact</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>To advocate self-government within British India</t>
+          <t>It was a rare moment of unity.</t>
         </is>
       </c>
     </row>
@@ -1996,97 +1996,97 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which agreement helped unite Hindus and Muslims for a common political goal in 1916?</t>
+          <t>Which act introduced provincial autonomy?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poona Pact</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Delhi Pact</t>
+          <t>Government of India Act 1919</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lucknow Pact</t>
+          <t>Government of India Act 1935</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Simla Agreement</t>
+          <t>Indian Independence Act 1947</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lucknow Pact</t>
+          <t>Government of India Act 1935</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>It was a rare moment of unity.</t>
+          <t>Allowed provinces more control in governance</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which British official was assassinated in retaliation of the Jallianwala Bagh massacre?</t>
+          <t>What was the main demand of the Home Rule League?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Complete Independence</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Michael O’Dwyer</t>
+          <t>Religious reforms</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Social equality</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Self-government within British Empire</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Michael O’Dwyer</t>
+          <t>Self-government within British Empire</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>He ordered Dyer’s actions and was killed by Udham Singh</t>
+          <t>It was a moderate demand for autonomy.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which leader was associated with the extremist faction of Congress?</t>
+          <t>Who launched the Home Rule League in 1916?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2096,377 +2096,377 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Believed in assertive and confrontational methods</t>
+          <t>To advocate self-government within British India</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The partition of Bengal was annulled in which year?</t>
+          <t>Who was associated with the foundation of the Home Rule League in 1916?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Subhash Chandra Bose</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Due to mass opposition, the British reversed the decision.</t>
+          <t>He started the league to demand self-government.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The All India Home Rule League was founded in 1916 by</t>
+          <t>Which British official was assassinated by Madan Lal Dhingra in London (1909)?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Lord Hardinge</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Curzon Wyllie</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Motilal Nehru</t>
+          <t>Lord Minto</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose</t>
+          <t>General Dyer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Curzon Wyllie</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Both worked parallelly for the same cause.</t>
+          <t>This was an early act of revolutionary nationalism.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Who was the Governor-General during the First Round Table Conference?</t>
+          <t>Which leader was associated with the extremist school of thought?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lord Willingdon</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lord Wavell</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>It was held in London in 1930</t>
+          <t>He believed "Swaraj is my birthright."</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Who wrote ‘Hind Swaraj’?</t>
+          <t>In which year was the Non-Cooperation Movement launched?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Book advocating self-rule and non-violence</t>
+          <t>Started by Gandhi to oppose Rowlatt Act and Jallianwala Bagh massacre</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which act gave Indians limited role in the administration for the first time?</t>
+          <t>Who gave the slogan “Do or Die” during the Quit India Movement?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1861</t>
+          <t>Bose</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1892</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Also known as Morley-Minto Reforms, introduced separate electorates</t>
+          <t>Urged Indians to fight for freedom at all costs</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which act allowed the British government to imprison people without trial in 1919?</t>
+          <t>The ‘extremists’ within Congress used which of the following strategies?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Government of India Act 1919</t>
+          <t>Petitions</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Peaceful protests</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Constitutional methods</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defence of India Act</t>
+          <t>Boycott and Swadeshi</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Boycott and Swadeshi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>It curtailed civil liberties and was opposed widely.</t>
+          <t>They rejected soft methods of the moderates.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which movement aimed to boycott foreign goods and promote Indian industries?</t>
+          <t>Who was the Viceroy of India during the Jallianwala Bagh massacre?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Quit India</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Lord Hardinge</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Non-Cooperation</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Civil Disobedience</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Focused on economic self-reliance</t>
+          <t>He was the British Governor-General when the tragedy occurred</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who founded the Swaraj Party in 1923?</t>
+          <t>Who presided over the Indian National Congress session in 1906 and gave the call for “Swaraj”?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gandhi and Nehru</t>
+          <t>Dada Bhai Naoroji</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Motilal Nehru and C.R. Das</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose and Rajendra Prasad</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Motilal Nehru and C.R. Das</t>
+          <t>Dada Bhai Naoroji</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>They wanted to enter legislative councils and wreck them from within</t>
+          <t>He officially demanded self-rule.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What was the purpose of the Montagu Declaration of 1917?</t>
+          <t>Which British official was assassinated in retaliation of the Jallianwala Bagh massacre?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Indianization of Army</t>
+          <t>Michael O’Dwyer</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Increasing salaries of officials</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gradual development of self-government</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gradual development of self-government</t>
+          <t>Michael O’Dwyer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>A vague promise made by the British.</t>
+          <t>He ordered Dyer’s actions and was killed by Udham Singh</t>
         </is>
       </c>
     </row>

--- a/Data/MH_StruggleofSwaraj.xlsx
+++ b/Data/MH_StruggleofSwaraj.xlsx
@@ -472,16 +472,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Congress leader was known as the 'Lion of Punjab'?</t>
+          <t>Who presided over the Indian National Congress session in 1906 and gave the call for “Swaraj”?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bhagat Singh</t>
+          <t>Dada Bhai Naoroji</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,392 +491,392 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Tilak</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Lala Lajpat Rai</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tilak</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Dada Bhai Naoroji</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>For his fiery speeches and nationalism</t>
+          <t>He officially demanded self-rule.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which party did Subhas Chandra Bose form after resigning from Congress?</t>
+          <t>Who was the Governor-General during the First Round Table Conference?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ghadar Party</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Swaraj Party</t>
+          <t>Lord Willingdon</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Indian National Army</t>
+          <t>Lord Wavell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Formed to continue revolutionary methods</t>
+          <t>It was held in London in 1930</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which was the last major movement before India’s independence?</t>
+          <t>The partition of Bengal was annulled in which year?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Non-Cooperation</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Launched in 1942 demanding end of British rule</t>
+          <t>Due to mass opposition, the British reversed the decision.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What was the main objective of the Swadeshi Movement?</t>
+          <t>Which revolutionaries were involved in the Alipore Bomb case (1908)?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>To demand Dominion status</t>
+          <t>Bhagat Singh and Rajguru</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To boycott British goods and promote Indian industries</t>
+          <t>Aurobindo Ghosh and his brother</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>To demand reservation</t>
+          <t>Mangal Pandey and Azad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>To oppose the salt tax</t>
+          <t>Bose and Dhingra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>To boycott British goods and promote Indian industries</t>
+          <t>Aurobindo Ghosh and his brother</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>It aimed at economic self-reliance.</t>
+          <t>They were accused of planning a bomb attack on a British judge.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The partition of Bengal was annulled in which year?</t>
+          <t>Which was the last major movement before India’s independence?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>Non-Cooperation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Due to mass opposition, the British reversed the decision.</t>
+          <t>Launched in 1942 demanding end of British rule</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who wrote the book ‘Hind Swaraj’?</t>
+          <t>Which movement aimed to boycott foreign goods and promote Indian industries?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Quit India</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Non-Cooperation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Civil Disobedience</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>He outlined his vision of self-rule.</t>
+          <t>Focused on economic self-reliance</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which group was most influenced by socialist ideas during the freedom struggle?</t>
+          <t>The ‘extremists’ within Congress used which of the following strategies?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Petitions</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Muslim League</t>
+          <t>Peaceful protests</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>Constitutional methods</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Boycott and Swadeshi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Boycott and Swadeshi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Subhas Bose was heavily inspired by socialism</t>
+          <t>They rejected soft methods of the moderates.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which revolutionaries were involved in the Alipore Bomb case (1908)?</t>
+          <t>What was the purpose of the Montagu Declaration of 1917?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bhagat Singh and Rajguru</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aurobindo Ghosh and his brother</t>
+          <t>Indianization of Army</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mangal Pandey and Azad</t>
+          <t>Increasing salaries of officials</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bose and Dhingra</t>
+          <t>Gradual development of self-government</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Aurobindo Ghosh and his brother</t>
+          <t>Gradual development of self-government</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>They were accused of planning a bomb attack on a British judge.</t>
+          <t>A vague promise made by the British.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which movement marked Mahatma Gandhi’s first active involvement in Indian politics?</t>
+          <t>Which movement was suspended after the Chauri Chaura incident?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rowlatt Satyagraha</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kheda Satyagraha</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dandi March</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>He fought for the rights of indigo farmers.</t>
+          <t>Gandhi called off the movement due to violence</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which of these was NOT a demand of the Congress in the early 20th century?</t>
+          <t>Who led the extremist faction during the split at the Surat session of Congress in 1907?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dominion status</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Civil rights</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Reduction of military expenditure</t>
+          <t>Motilal Nehru</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>This became a goal only after 1929</t>
+          <t>The extremists wanted aggressive methods for freedom.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Who termed the Montagu-Chelmsford Reforms as “unworthy of England to offer and India to accept”?</t>
+          <t>Who was associated with the foundation of the Home Rule League in 1916?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -886,587 +886,587 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Gopal Krishna Gokhale</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Mahatma Gandhi</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Annie Besant</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Subhash Chandra Bose</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>He criticized the reforms for being inadequate.</t>
+          <t>He started the league to demand self-government.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The ‘Moderates’ and ‘Extremists’ of Congress reunited in which session?</t>
+          <t>What was the main objective of the Swadeshi Movement?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Surat Session 1907</t>
+          <t>To demand Dominion status</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lucknow Session 1916</t>
+          <t>To boycott British goods and promote Indian industries</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Calcutta Session 1906</t>
+          <t>To demand reservation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>To oppose the salt tax</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lucknow Session 1916</t>
+          <t>To boycott British goods and promote Indian industries</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A key unity moment in the freedom struggle.</t>
+          <t>It aimed at economic self-reliance.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which session of Congress declared Purna Swaraj as the goal?</t>
+          <t>Which of these was NOT a demand of the Congress in the early 20th century?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bombay Session 1918</t>
+          <t>Dominion status</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Calcutta Session 1920</t>
+          <t>Civil rights</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nagpur Session 1921</t>
+          <t>Reduction of military expenditure</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>It declared complete independence as the goal of INC</t>
+          <t>This became a goal only after 1929</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What was the purpose of the Montagu Declaration of 1917?</t>
+          <t>Which event led to Gandhi’s entry into Indian politics?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Jallianwala Bagh</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Indianization of Army</t>
+          <t>Champaran Satyagraha</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Increasing salaries of officials</t>
+          <t>Khilafat Movement</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gradual development of self-government</t>
+          <t>Simon Commission</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gradual development of self-government</t>
+          <t>Champaran Satyagraha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>A vague promise made by the British.</t>
+          <t>To address indigo farmers' plight</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The All India Home Rule League was founded in 1916 by</t>
+          <t>Who was the first woman president of Indian National Congress?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Sarojini Naidu</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Annie Besant</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Tilak and Annie Besant</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Motilal Nehru</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose</t>
+          <t>Vijaya Lakshmi Pandit</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Both worked parallelly for the same cause.</t>
+          <t>She became president in 1917.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which event led to Gandhi’s entry into Indian politics?</t>
+          <t>Who launched the Home Rule League in 1916?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jallianwala Bagh</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Champaran Satyagraha</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Khilafat Movement</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Simon Commission</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Champaran Satyagraha</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>To address indigo farmers' plight</t>
+          <t>To advocate self-government within British India</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which organization aimed to promote political education and demand self-rule in India?</t>
+          <t>Which of the following was *not* a feature of Montagu-Chelmsford reforms?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arya Samaj</t>
+          <t>Introduction of Dyarchy</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Muslim League</t>
+          <t>Bicameral Legislature</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Home Rule League</t>
+          <t>Abolition of ICS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Indian National Army</t>
+          <t>Expansion of legislative councils</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Home Rule League</t>
+          <t>Abolition of ICS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>It educated people on political rights.</t>
+          <t>ICS was not abolished.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who led the extremist faction during the split at the Surat session of Congress in 1907?</t>
+          <t>Which British official was assassinated by Madan Lal Dhingra in London (1909)?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Lord Hardinge</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Curzon Wyllie</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Lord Minto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motilal Nehru</t>
+          <t>General Dyer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Curzon Wyllie</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The extremists wanted aggressive methods for freedom.</t>
+          <t>This was an early act of revolutionary nationalism.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What was the main aim of the Simon Commission?</t>
+          <t>The ‘Moderates’ and ‘Extremists’ of Congress reunited in which session?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>To partition Bengal</t>
+          <t>Surat Session 1907</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To assess the working of Government of India Act 1919</t>
+          <t>Lucknow Session 1916</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>To introduce Purna Swaraj</t>
+          <t>Calcutta Session 1906</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>To suppress revolutionaries</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>To assess the working of Government of India Act 1919</t>
+          <t>Lucknow Session 1916</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sent by British without Indian members</t>
+          <t>A key unity moment in the freedom struggle.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Lucknow Pact of 1916 was signed between which two political groups?</t>
+          <t>The Jallianwala Bagh massacre took place in which year?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Congress and British</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Congress and Muslim League</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Muslim League and British</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Congress and Home Rule League</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Congress and Muslim League</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>It was a historic agreement for Hindu-Muslim unity.</t>
+          <t>This tragic event shook the nation and turned the tide.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Who founded the Swaraj Party in 1923?</t>
+          <t>What was the main aim of the Simon Commission?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gandhi and Nehru</t>
+          <t>To partition Bengal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Motilal Nehru and C.R. Das</t>
+          <t>To assess the working of Government of India Act 1919</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>To introduce Purna Swaraj</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose and Rajendra Prasad</t>
+          <t>To suppress revolutionaries</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Motilal Nehru and C.R. Das</t>
+          <t>To assess the working of Government of India Act 1919</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>They wanted to enter legislative councils and wreck them from within</t>
+          <t>Sent by British without Indian members</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which leader was associated with the extremist faction of Congress?</t>
+          <t>Who gave the slogan “Do or Die” during the Quit India Movement?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gandhi</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Tilak</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Dadabhai Naoroji</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>M.G. Ranade</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Believed in assertive and confrontational methods</t>
+          <t>Urged Indians to fight for freedom at all costs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which movement was suspended after the Chauri Chaura incident?</t>
+          <t>In which year was the Non-Cooperation Movement launched?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Gandhi called off the movement due to violence</t>
+          <t>Started by Gandhi to oppose Rowlatt Act and Jallianwala Bagh massacre</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which movement began as a reaction to the Partition of Bengal in 1905?</t>
+          <t>Which act allowed the British government to imprison people without trial in 1919?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Government of India Act 1919</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Defence of India Act</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bengal was divided by the British, sparking a boycott and nationalistic movement.</t>
+          <t>It curtailed civil liberties and was opposed widely.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which act increased the number of Indians in the legislative council in 1909?</t>
+          <t>Which movement marked Mahatma Gandhi’s first active involvement in Indian politics?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Rowlatt Satyagraha</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Montagu Reforms</t>
+          <t>Kheda Satyagraha</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Indian Councils Act</t>
+          <t>Dandi March</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Also introduced separate electorates for Muslims.</t>
+          <t>He fought for the rights of indigo farmers.</t>
         </is>
       </c>
     </row>
@@ -1512,231 +1512,231 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Who wrote ‘Hind Swaraj’?</t>
+          <t>Which group was most influenced by socialist ideas during the freedom struggle?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Muslim League</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Book advocating self-rule and non-violence</t>
+          <t>Subhas Bose was heavily inspired by socialism</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which act gave Indians limited role in the administration for the first time?</t>
+          <t>Who was the Viceroy of India during the Jallianwala Bagh massacre?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1861</t>
+          <t>Lord Hardinge</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1892</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Also known as Morley-Minto Reforms, introduced separate electorates</t>
+          <t>He was the British Governor-General when the tragedy occurred</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which of the following was *not* a feature of Montagu-Chelmsford reforms?</t>
+          <t>Which act introduced provincial autonomy?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Introduction of Dyarchy</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bicameral Legislature</t>
+          <t>Government of India Act 1919</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Abolition of ICS</t>
+          <t>Government of India Act 1935</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Expansion of legislative councils</t>
+          <t>Indian Independence Act 1947</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Abolition of ICS</t>
+          <t>Government of India Act 1935</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ICS was not abolished.</t>
+          <t>Allowed provinces more control in governance</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Jallianwala Bagh massacre took place in which year?</t>
+          <t>Who wrote ‘Hind Swaraj’?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>This tragic event shook the nation and turned the tide.</t>
+          <t>Book advocating self-rule and non-violence</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which act allowed the British government to imprison people without trial in 1919?</t>
+          <t>Which act gave Indians limited role in the administration for the first time?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Government of India Act 1919</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Indian Councils Act 1861</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Indian Councils Act 1892</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Indian Councils Act 1909</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Defence of India Act</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>It curtailed civil liberties and was opposed widely.</t>
+          <t>Also known as Morley-Minto Reforms, introduced separate electorates</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The slogan 'Swaraj is my birthright' was given by?</t>
+          <t>Which leader was associated with the extremist school of thought?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Dadabhai Naoroji</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Gokhale</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Tilak</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Gandhi</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Nehru</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1746,727 +1746,727 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Assertive nationalist leader who inspired the youth</t>
+          <t>He believed "Swaraj is my birthright."</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which movement aimed to boycott foreign goods and promote Indian industries?</t>
+          <t>Which organization aimed to promote political education and demand self-rule in India?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Quit India</t>
+          <t>Arya Samaj</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Muslim League</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Non-Cooperation</t>
+          <t>Home Rule League</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Civil Disobedience</t>
+          <t>Indian National Army</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Home Rule League</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Focused on economic self-reliance</t>
+          <t>It educated people on political rights.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which movement first used mass mobilization in India?</t>
+          <t>The slogan 'Swaraj is my birthright' was given by?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Home Rule Movement</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>In protest of partition of Bengal 1905</t>
+          <t>Assertive nationalist leader who inspired the youth</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who was the first woman president of Indian National Congress?</t>
+          <t>Who termed the Montagu-Chelmsford Reforms as “unworthy of England to offer and India to accept”?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Mahatma Gandhi</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Annie Besant</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vijaya Lakshmi Pandit</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>She became president in 1917.</t>
+          <t>He criticized the reforms for being inadequate.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who was the Governor-General during the First Round Table Conference?</t>
+          <t>Which agreement helped unite Hindus and Muslims for a common political goal in 1916?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Poona Pact</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lord Willingdon</t>
+          <t>Delhi Pact</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Lucknow Pact</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lord Wavell</t>
+          <t>Simla Agreement</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Lucknow Pact</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>It was held in London in 1930</t>
+          <t>It was a rare moment of unity.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What was the outcome of the Gandhi-Irwin Pact?</t>
+          <t>Which leader was associated with the extremist faction of Congress?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>British granted independence</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Salt law repealed</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>End of Civil Disobedience temporarily</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Constitution formed</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>End of Civil Disobedience temporarily</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Also allowed peaceful picketing</t>
+          <t>Believed in assertive and confrontational methods</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which agreement helped unite Hindus and Muslims for a common political goal in 1916?</t>
+          <t>Which movement began as a reaction to the Partition of Bengal in 1905?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poona Pact</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Delhi Pact</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lucknow Pact</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Simla Agreement</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lucknow Pact</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>It was a rare moment of unity.</t>
+          <t>Bengal was divided by the British, sparking a boycott and nationalistic movement.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which act introduced provincial autonomy?</t>
+          <t>What was the main demand of the Home Rule League?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Complete Independence</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Government of India Act 1919</t>
+          <t>Religious reforms</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Government of India Act 1935</t>
+          <t>Social equality</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Indian Independence Act 1947</t>
+          <t>Self-government within British Empire</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Government of India Act 1935</t>
+          <t>Self-government within British Empire</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Allowed provinces more control in governance</t>
+          <t>It was a moderate demand for autonomy.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What was the main demand of the Home Rule League?</t>
+          <t>Which movement first used mass mobilization in India?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Complete Independence</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Religious reforms</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Social equality</t>
+          <t>Home Rule Movement</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Self-government within British Empire</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Self-government within British Empire</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>It was a moderate demand for autonomy.</t>
+          <t>In protest of partition of Bengal 1905</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who launched the Home Rule League in 1916?</t>
+          <t>Who founded the Swaraj Party in 1923?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Gandhi and Nehru</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Motilal Nehru and C.R. Das</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Subhash Chandra Bose and Rajendra Prasad</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Motilal Nehru and C.R. Das</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>To advocate self-government within British India</t>
+          <t>They wanted to enter legislative councils and wreck them from within</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who was associated with the foundation of the Home Rule League in 1916?</t>
+          <t>Who wrote the book ‘Hind Swaraj’?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Gopal Krishna Gokhale</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Annie Besant</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Mahatma Gandhi</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Gopal Krishna Gokhale</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Mahatma Gandhi</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Subhash Chandra Bose</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Bal Gangadhar Tilak</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>He started the league to demand self-government.</t>
+          <t>He outlined his vision of self-rule.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which British official was assassinated by Madan Lal Dhingra in London (1909)?</t>
+          <t>What was the outcome of the Gandhi-Irwin Pact?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lord Hardinge</t>
+          <t>British granted independence</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Curzon Wyllie</t>
+          <t>Salt law repealed</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lord Minto</t>
+          <t>End of Civil Disobedience temporarily</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>General Dyer</t>
+          <t>Constitution formed</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Curzon Wyllie</t>
+          <t>End of Civil Disobedience temporarily</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>This was an early act of revolutionary nationalism.</t>
+          <t>Also allowed peaceful picketing</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which leader was associated with the extremist school of thought?</t>
+          <t>Which British official was assassinated in retaliation of the Jallianwala Bagh massacre?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Michael O’Dwyer</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Michael O’Dwyer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>He believed "Swaraj is my birthright."</t>
+          <t>He ordered Dyer’s actions and was killed by Udham Singh</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>In which year was the Non-Cooperation Movement launched?</t>
+          <t>Which Congress leader was known as the 'Lion of Punjab'?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Bhagat Singh</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Started by Gandhi to oppose Rowlatt Act and Jallianwala Bagh massacre</t>
+          <t>For his fiery speeches and nationalism</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Who gave the slogan “Do or Die” during the Quit India Movement?</t>
+          <t>The Lucknow Pact of 1916 was signed between which two political groups?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>Congress and British</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bose</t>
+          <t>Congress and Muslim League</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Muslim League and British</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Congress and Home Rule League</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Congress and Muslim League</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Urged Indians to fight for freedom at all costs</t>
+          <t>It was a historic agreement for Hindu-Muslim unity.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The ‘extremists’ within Congress used which of the following strategies?</t>
+          <t>Which party did Subhas Chandra Bose form after resigning from Congress?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Petitions</t>
+          <t>Ghadar Party</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Peaceful protests</t>
+          <t>Swaraj Party</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Constitutional methods</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Boycott and Swadeshi</t>
+          <t>Indian National Army</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Boycott and Swadeshi</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>They rejected soft methods of the moderates.</t>
+          <t>Formed to continue revolutionary methods</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Who was the Viceroy of India during the Jallianwala Bagh massacre?</t>
+          <t>The All India Home Rule League was founded in 1916 by</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lord Hardinge</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Motilal Nehru</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Subhash Chandra Bose</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>He was the British Governor-General when the tragedy occurred</t>
+          <t>Both worked parallelly for the same cause.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who presided over the Indian National Congress session in 1906 and gave the call for “Swaraj”?</t>
+          <t>Which session of Congress declared Purna Swaraj as the goal?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dada Bhai Naoroji</t>
+          <t>Bombay Session 1918</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Calcutta Session 1920</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Nagpur Session 1921</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dada Bhai Naoroji</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>He officially demanded self-rule.</t>
+          <t>It declared complete independence as the goal of INC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which British official was assassinated in retaliation of the Jallianwala Bagh massacre?</t>
+          <t>Which act increased the number of Indians in the legislative council in 1909?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Michael O’Dwyer</t>
+          <t>Montagu Reforms</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Indian Councils Act</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Michael O’Dwyer</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>He ordered Dyer’s actions and was killed by Udham Singh</t>
+          <t>Also introduced separate electorates for Muslims.</t>
         </is>
       </c>
     </row>

--- a/Data/MH_StruggleofSwaraj.xlsx
+++ b/Data/MH_StruggleofSwaraj.xlsx
@@ -472,121 +472,121 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who presided over the Indian National Congress session in 1906 and gave the call for “Swaraj”?</t>
+          <t>Who founded the Swaraj Party in 1923?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dada Bhai Naoroji</t>
+          <t>Gandhi and Nehru</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Motilal Nehru and C.R. Das</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Subhash Chandra Bose and Rajendra Prasad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dada Bhai Naoroji</t>
+          <t>Motilal Nehru and C.R. Das</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>He officially demanded self-rule.</t>
+          <t>They wanted to enter legislative councils and wreck them from within</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Who was the Governor-General during the First Round Table Conference?</t>
+          <t>Who wrote the book ‘Hind Swaraj’?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lord Willingdon</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lord Wavell</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>It was held in London in 1930</t>
+          <t>He outlined his vision of self-rule.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The partition of Bengal was annulled in which year?</t>
+          <t>What was the outcome of the Gandhi-Irwin Pact?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>British granted independence</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>Salt law repealed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>End of Civil Disobedience temporarily</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Constitution formed</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>End of Civil Disobedience temporarily</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Due to mass opposition, the British reversed the decision.</t>
+          <t>Also allowed peaceful picketing</t>
         </is>
       </c>
     </row>
@@ -596,677 +596,677 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which revolutionaries were involved in the Alipore Bomb case (1908)?</t>
+          <t>Which British official was assassinated in retaliation of the Jallianwala Bagh massacre?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bhagat Singh and Rajguru</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aurobindo Ghosh and his brother</t>
+          <t>Michael O’Dwyer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mangal Pandey and Azad</t>
+          <t>Lord Chelmsford</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bose and Dhingra</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aurobindo Ghosh and his brother</t>
+          <t>Michael O’Dwyer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>They were accused of planning a bomb attack on a British judge.</t>
+          <t>He ordered Dyer’s actions and was killed by Udham Singh</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which was the last major movement before India’s independence?</t>
+          <t>Which Congress leader was known as the 'Lion of Punjab'?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Bhagat Singh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Non-Cooperation</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Launched in 1942 demanding end of British rule</t>
+          <t>For his fiery speeches and nationalism</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which movement aimed to boycott foreign goods and promote Indian industries?</t>
+          <t>The Lucknow Pact of 1916 was signed between which two political groups?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quit India</t>
+          <t>Congress and British</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Congress and Muslim League</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Non-Cooperation</t>
+          <t>Muslim League and British</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Civil Disobedience</t>
+          <t>Congress and Home Rule League</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Congress and Muslim League</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Focused on economic self-reliance</t>
+          <t>It was a historic agreement for Hindu-Muslim unity.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The ‘extremists’ within Congress used which of the following strategies?</t>
+          <t>Which party did Subhas Chandra Bose form after resigning from Congress?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Petitions</t>
+          <t>Ghadar Party</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Peaceful protests</t>
+          <t>Swaraj Party</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Constitutional methods</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boycott and Swadeshi</t>
+          <t>Indian National Army</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Boycott and Swadeshi</t>
+          <t>Forward Bloc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>They rejected soft methods of the moderates.</t>
+          <t>Formed to continue revolutionary methods</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What was the purpose of the Montagu Declaration of 1917?</t>
+          <t>The All India Home Rule League was founded in 1916 by</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Indianization of Army</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Increasing salaries of officials</t>
+          <t>Motilal Nehru</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gradual development of self-government</t>
+          <t>Subhash Chandra Bose</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gradual development of self-government</t>
+          <t>Tilak and Annie Besant</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>A vague promise made by the British.</t>
+          <t>Both worked parallelly for the same cause.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which movement was suspended after the Chauri Chaura incident?</t>
+          <t>Which session of Congress declared Purna Swaraj as the goal?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Bombay Session 1918</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Calcutta Session 1920</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Nagpur Session 1921</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Gandhi called off the movement due to violence</t>
+          <t>It declared complete independence as the goal of INC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Who led the extremist faction during the split at the Surat session of Congress in 1907?</t>
+          <t>Which act increased the number of Indians in the legislative council in 1909?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Montagu Reforms</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motilal Nehru</t>
+          <t>Indian Councils Act</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>The extremists wanted aggressive methods for freedom.</t>
+          <t>Also introduced separate electorates for Muslims.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Who was associated with the foundation of the Home Rule League in 1916?</t>
+          <t>Which act gave Indians limited role in the administration for the first time?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Indian Councils Act 1861</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Indian Councils Act 1892</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Indian Councils Act 1909</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>He started the league to demand self-government.</t>
+          <t>Also known as Morley-Minto Reforms, introduced separate electorates</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What was the main objective of the Swadeshi Movement?</t>
+          <t>Which leader was associated with the extremist school of thought?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>To demand Dominion status</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To boycott British goods and promote Indian industries</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>To demand reservation</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>To oppose the salt tax</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>To boycott British goods and promote Indian industries</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>It aimed at economic self-reliance.</t>
+          <t>He believed "Swaraj is my birthright."</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which of these was NOT a demand of the Congress in the early 20th century?</t>
+          <t>Which organization aimed to promote political education and demand self-rule in India?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dominion status</t>
+          <t>Arya Samaj</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Muslim League</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Civil rights</t>
+          <t>Home Rule League</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reduction of military expenditure</t>
+          <t>Indian National Army</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Home Rule League</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>This became a goal only after 1929</t>
+          <t>It educated people on political rights.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which event led to Gandhi’s entry into Indian politics?</t>
+          <t>The slogan 'Swaraj is my birthright' was given by?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jallianwala Bagh</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Champaran Satyagraha</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Khilafat Movement</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Simon Commission</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Champaran Satyagraha</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>To address indigo farmers' plight</t>
+          <t>Assertive nationalist leader who inspired the youth</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who was the first woman president of Indian National Congress?</t>
+          <t>Who termed the Montagu-Chelmsford Reforms as “unworthy of England to offer and India to accept”?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Mahatma Gandhi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Annie Besant</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vijaya Lakshmi Pandit</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>She became president in 1917.</t>
+          <t>He criticized the reforms for being inadequate.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who launched the Home Rule League in 1916?</t>
+          <t>Which agreement helped unite Hindus and Muslims for a common political goal in 1916?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Poona Pact</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Delhi Pact</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Lucknow Pact</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Simla Agreement</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Lucknow Pact</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>To advocate self-government within British India</t>
+          <t>It was a rare moment of unity.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which of the following was *not* a feature of Montagu-Chelmsford reforms?</t>
+          <t>Which leader was associated with the extremist faction of Congress?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Introduction of Dyarchy</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bicameral Legislature</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Abolition of ICS</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Expansion of legislative councils</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Abolition of ICS</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ICS was not abolished.</t>
+          <t>Believed in assertive and confrontational methods</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which British official was assassinated by Madan Lal Dhingra in London (1909)?</t>
+          <t>Which movement began as a reaction to the Partition of Bengal in 1905?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lord Hardinge</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Curzon Wyllie</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lord Minto</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>General Dyer</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Curzon Wyllie</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>This was an early act of revolutionary nationalism.</t>
+          <t>Bengal was divided by the British, sparking a boycott and nationalistic movement.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The ‘Moderates’ and ‘Extremists’ of Congress reunited in which session?</t>
+          <t>What was the main demand of the Home Rule League?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Surat Session 1907</t>
+          <t>Complete Independence</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lucknow Session 1916</t>
+          <t>Religious reforms</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcutta Session 1906</t>
+          <t>Social equality</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Self-government within British Empire</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lucknow Session 1916</t>
+          <t>Self-government within British Empire</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>A key unity moment in the freedom struggle.</t>
+          <t>It was a moderate demand for autonomy.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Jallianwala Bagh massacre took place in which year?</t>
+          <t>Which movement first used mass mobilization in India?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Home Rule Movement</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>This tragic event shook the nation and turned the tide.</t>
+          <t>In protest of partition of Bengal 1905</t>
         </is>
       </c>
     </row>
@@ -1672,521 +1672,521 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which act gave Indians limited role in the administration for the first time?</t>
+          <t>Who was associated with the foundation of the Home Rule League in 1916?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1861</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1892</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Subhash Chandra Bose</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1909</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Also known as Morley-Minto Reforms, introduced separate electorates</t>
+          <t>He started the league to demand self-government.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which leader was associated with the extremist school of thought?</t>
+          <t>What was the main objective of the Swadeshi Movement?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>To demand Dominion status</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>To boycott British goods and promote Indian industries</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>To demand reservation</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>To oppose the salt tax</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>To boycott British goods and promote Indian industries</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>He believed "Swaraj is my birthright."</t>
+          <t>It aimed at economic self-reliance.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which organization aimed to promote political education and demand self-rule in India?</t>
+          <t>Which of these was NOT a demand of the Congress in the early 20th century?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arya Samaj</t>
+          <t>Dominion status</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Muslim League</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Home Rule League</t>
+          <t>Civil rights</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Indian National Army</t>
+          <t>Reduction of military expenditure</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Home Rule League</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>It educated people on political rights.</t>
+          <t>This became a goal only after 1929</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The slogan 'Swaraj is my birthright' was given by?</t>
+          <t>Which event led to Gandhi’s entry into Indian politics?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Jallianwala Bagh</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Champaran Satyagraha</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>Khilafat Movement</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Simon Commission</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Champaran Satyagraha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Assertive nationalist leader who inspired the youth</t>
+          <t>To address indigo farmers' plight</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who termed the Montagu-Chelmsford Reforms as “unworthy of England to offer and India to accept”?</t>
+          <t>Who was the first woman president of Indian National Congress?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vijaya Lakshmi Pandit</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>Annie Besant</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Lala Lajpat Rai</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Mahatma Gandhi</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>He criticized the reforms for being inadequate.</t>
+          <t>She became president in 1917.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which agreement helped unite Hindus and Muslims for a common political goal in 1916?</t>
+          <t>Who launched the Home Rule League in 1916?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poona Pact</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Delhi Pact</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lucknow Pact</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Simla Agreement</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lucknow Pact</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>It was a rare moment of unity.</t>
+          <t>To advocate self-government within British India</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which leader was associated with the extremist faction of Congress?</t>
+          <t>Which of the following was *not* a feature of Montagu-Chelmsford reforms?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Introduction of Dyarchy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Bicameral Legislature</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Abolition of ICS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>Expansion of legislative councils</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Abolition of ICS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Believed in assertive and confrontational methods</t>
+          <t>ICS was not abolished.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which movement began as a reaction to the Partition of Bengal in 1905?</t>
+          <t>Which British official was assassinated by Madan Lal Dhingra in London (1909)?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>Lord Hardinge</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>Curzon Wyllie</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Lord Minto</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quit India Movement</t>
+          <t>General Dyer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Curzon Wyllie</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bengal was divided by the British, sparking a boycott and nationalistic movement.</t>
+          <t>This was an early act of revolutionary nationalism.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What was the main demand of the Home Rule League?</t>
+          <t>The ‘Moderates’ and ‘Extremists’ of Congress reunited in which session?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Complete Independence</t>
+          <t>Surat Session 1907</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Religious reforms</t>
+          <t>Lucknow Session 1916</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Social equality</t>
+          <t>Calcutta Session 1906</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Self-government within British Empire</t>
+          <t>Lahore Session 1929</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Self-government within British Empire</t>
+          <t>Lucknow Session 1916</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>It was a moderate demand for autonomy.</t>
+          <t>A key unity moment in the freedom struggle.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which movement first used mass mobilization in India?</t>
+          <t>The Jallianwala Bagh massacre took place in which year?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Civil Disobedience Movement</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Home Rule Movement</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Non-Cooperation Movement</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>In protest of partition of Bengal 1905</t>
+          <t>This tragic event shook the nation and turned the tide.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who founded the Swaraj Party in 1923?</t>
+          <t>Who presided over the Indian National Congress session in 1906 and gave the call for “Swaraj”?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gandhi and Nehru</t>
+          <t>Dada Bhai Naoroji</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Motilal Nehru and C.R. Das</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose and Rajendra Prasad</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Motilal Nehru and C.R. Das</t>
+          <t>Dada Bhai Naoroji</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>They wanted to enter legislative councils and wreck them from within</t>
+          <t>He officially demanded self-rule.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who wrote the book ‘Hind Swaraj’?</t>
+          <t>Who was the Governor-General during the First Round Table Conference?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Lord Willingdon</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Lord Wavell</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Lord Irwin</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>He outlined his vision of self-rule.</t>
+          <t>It was held in London in 1930</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What was the outcome of the Gandhi-Irwin Pact?</t>
+          <t>The partition of Bengal was annulled in which year?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>British granted independence</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Salt law repealed</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>End of Civil Disobedience temporarily</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Constitution formed</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>End of Civil Disobedience temporarily</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Also allowed peaceful picketing</t>
+          <t>Due to mass opposition, the British reversed the decision.</t>
         </is>
       </c>
     </row>
@@ -2196,277 +2196,277 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which British official was assassinated in retaliation of the Jallianwala Bagh massacre?</t>
+          <t>Which revolutionaries were involved in the Alipore Bomb case (1908)?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Bhagat Singh and Rajguru</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Michael O’Dwyer</t>
+          <t>Aurobindo Ghosh and his brother</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lord Chelmsford</t>
+          <t>Mangal Pandey and Azad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lord Irwin</t>
+          <t>Bose and Dhingra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Michael O’Dwyer</t>
+          <t>Aurobindo Ghosh and his brother</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>He ordered Dyer’s actions and was killed by Udham Singh</t>
+          <t>They were accused of planning a bomb attack on a British judge.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Congress leader was known as the 'Lion of Punjab'?</t>
+          <t>Which was the last major movement before India’s independence?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bhagat Singh</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Non-Cooperation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>For his fiery speeches and nationalism</t>
+          <t>Launched in 1942 demanding end of British rule</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Lucknow Pact of 1916 was signed between which two political groups?</t>
+          <t>Which movement aimed to boycott foreign goods and promote Indian industries?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Congress and British</t>
+          <t>Quit India</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Congress and Muslim League</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Muslim League and British</t>
+          <t>Non-Cooperation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Congress and Home Rule League</t>
+          <t>Civil Disobedience</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Congress and Muslim League</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>It was a historic agreement for Hindu-Muslim unity.</t>
+          <t>Focused on economic self-reliance</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which party did Subhas Chandra Bose form after resigning from Congress?</t>
+          <t>The ‘extremists’ within Congress used which of the following strategies?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ghadar Party</t>
+          <t>Petitions</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Swaraj Party</t>
+          <t>Peaceful protests</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Constitutional methods</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Indian National Army</t>
+          <t>Boycott and Swadeshi</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Forward Bloc</t>
+          <t>Boycott and Swadeshi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Formed to continue revolutionary methods</t>
+          <t>They rejected soft methods of the moderates.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The All India Home Rule League was founded in 1916 by</t>
+          <t>What was the purpose of the Montagu Declaration of 1917?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Indianization of Army</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Motilal Nehru</t>
+          <t>Increasing salaries of officials</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Subhash Chandra Bose</t>
+          <t>Gradual development of self-government</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tilak and Annie Besant</t>
+          <t>Gradual development of self-government</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Both worked parallelly for the same cause.</t>
+          <t>A vague promise made by the British.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which session of Congress declared Purna Swaraj as the goal?</t>
+          <t>Which movement was suspended after the Chauri Chaura incident?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bombay Session 1918</t>
+          <t>Civil Disobedience Movement</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Quit India Movement</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Calcutta Session 1920</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nagpur Session 1921</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lahore Session 1929</t>
+          <t>Non-Cooperation Movement</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>It declared complete independence as the goal of INC</t>
+          <t>Gandhi called off the movement due to violence</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which act increased the number of Indians in the legislative council in 1909?</t>
+          <t>Who led the extremist faction during the split at the Surat session of Congress in 1907?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Montagu Reforms</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Indian Councils Act</t>
+          <t>Motilal Nehru</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Also introduced separate electorates for Muslims.</t>
+          <t>The extremists wanted aggressive methods for freedom.</t>
         </is>
       </c>
     </row>
